--- a/modules/apperp/management-aset/resources/laporan/daftar-work-order/standar.xlsx
+++ b/modules/apperp/management-aset/resources/laporan/daftar-work-order/standar.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>${kop.logo_kiri}</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>${dicetak_pada}</t>
+  </si>
+  <si>
+    <t>Filter tambahan</t>
+  </si>
+  <si>
+    <t>${filter_tambahan}</t>
   </si>
   <si>
     <t>Nomor</t>
@@ -670,92 +676,100 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
